--- a/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_TQ-CB PRAT.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_TQ-CB PRAT.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -775,7 +775,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -787,67 +787,67 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>7.0602</v>
+        <v>4.7221</v>
       </c>
       <c r="E5" t="n">
-        <v>7.0602</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4.0301</v>
       </c>
       <c r="G5" t="n">
-        <v>7.0602</v>
+        <v>5.814299999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9178</v>
+        <v>2.3289</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1425</v>
+        <v>3.4853</v>
       </c>
       <c r="J5" t="n">
-        <v>7.0602</v>
+        <v>4.9216</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9178</v>
+        <v>1.7625</v>
       </c>
       <c r="L5" t="n">
-        <v>4.1425</v>
+        <v>3.1591</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.8926999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.5664</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.3264000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.6163999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-5.3425</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>4.726</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.0105</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.1129</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.8975000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-2.4863</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.4863</v>
       </c>
     </row>
     <row r="6">
@@ -931,7 +931,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. CARREÑO VIDAL</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -940,76 +940,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>3.5425</v>
+        <v>1.743</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5425</v>
+        <v>3.54</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-1.797</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5425</v>
+        <v>-0.3615</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5836</v>
+        <v>5.6056</v>
       </c>
       <c r="I7" t="n">
-        <v>2.959</v>
+        <v>-5.9671</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5425</v>
+        <v>5.9085</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5836</v>
+        <v>7.4053</v>
       </c>
       <c r="L7" t="n">
-        <v>2.959</v>
+        <v>-1.497</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-6.27</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.7996</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-4.4704</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.8494</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-7.191800000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>5.342499999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.7346</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.2276</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.507</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2192000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.5959</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.3767</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>G. MONTOYA SOLANILLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1018,40 +1018,40 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.9343</v>
+        <v>0.1896</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9343</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>0.1896</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1419</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1419</v>
+      </c>
+      <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" t="n">
-        <v>2.9343</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.7507</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.1836</v>
-      </c>
       <c r="J8" t="n">
-        <v>2.9343</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7507</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1836</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.1419</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.1419</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1066,13 +1066,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.0477</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.0477</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1087,7 +1087,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. GARCIA RIERA</t>
+          <t>S. CAMPBELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1099,73 +1099,73 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.787900000000001</v>
+        <v>0.07259999999999994</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2423</v>
+        <v>1.0242</v>
       </c>
       <c r="F9" t="n">
-        <v>4.0301</v>
+        <v>-0.9516</v>
       </c>
       <c r="G9" t="n">
-        <v>2.88</v>
+        <v>-0.6665000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5782999999999998</v>
+        <v>-0.3723</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3018</v>
+        <v>-0.2943</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9873</v>
+        <v>-0.1585000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01190000000000002</v>
+        <v>-0.4347</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9755</v>
+        <v>0.2762</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8926999999999999</v>
+        <v>-0.5080999999999998</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5664</v>
+        <v>0.06240000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3264000000000001</v>
+        <v>-0.5705</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6163999999999999</v>
+        <v>2.0548</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.3425</v>
+        <v>-1.0274</v>
       </c>
       <c r="R9" t="n">
-        <v>4.726</v>
+        <v>3.0822</v>
       </c>
       <c r="S9" t="n">
-        <v>2.0105</v>
+        <v>1.2802</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1129</v>
+        <v>0.7923</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8975000000000001</v>
+        <v>0.488</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4863</v>
+        <v>-2.5959</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.4178</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4863</v>
+        <v>-4.0137</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>K. KELIKI EBENGO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1177,73 +1177,73 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1.743</v>
+        <v>-0.802</v>
       </c>
       <c r="E10" t="n">
-        <v>3.54</v>
+        <v>-0.633</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.797</v>
+        <v>-0.1689</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3615</v>
+        <v>0.7383</v>
       </c>
       <c r="H10" t="n">
-        <v>5.6056</v>
+        <v>-0.3489</v>
       </c>
       <c r="I10" t="n">
-        <v>-5.9671</v>
+        <v>1.0869</v>
       </c>
       <c r="J10" t="n">
-        <v>5.9085</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>7.4053</v>
+        <v>0.351</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.497</v>
+        <v>0.3945</v>
       </c>
       <c r="M10" t="n">
-        <v>-6.27</v>
+        <v>-0.007300000000000029</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7996</v>
+        <v>-0.6998</v>
       </c>
       <c r="O10" t="n">
-        <v>-4.4704</v>
+        <v>0.6924</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8494</v>
+        <v>-1.2328</v>
       </c>
       <c r="Q10" t="n">
-        <v>-7.191800000000001</v>
+        <v>-3.0822</v>
       </c>
       <c r="R10" t="n">
-        <v>5.342499999999999</v>
+        <v>1.8494</v>
       </c>
       <c r="S10" t="n">
-        <v>3.7346</v>
+        <v>0.8707</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2276</v>
+        <v>0.9843999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>1.507</v>
+        <v>-0.1136</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2192000000000001</v>
+        <v>-1.178</v>
       </c>
       <c r="W10" t="n">
-        <v>2.5959</v>
+        <v>0.7192</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3767</v>
+        <v>-1.8972</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. MONTOYA SOLANILLA</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1252,76 +1252,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1896</v>
+        <v>-1.1641</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-1.7608</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1896</v>
+        <v>0.5966000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1419</v>
+        <v>-3.8629</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1419</v>
+        <v>-2.0252</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-1.8378</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.7657</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-1.1248</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.3590999999999998</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1419</v>
+        <v>-3.0972</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1419</v>
+        <v>-0.9004</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-2.1968</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.8493</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-3.0822</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4.9315</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0477</v>
+        <v>-0.4586</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-0.6387999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0477</v>
+        <v>0.1801</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.3081</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.7259</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.4178</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. CAMPBELL</t>
+          <t>P. CARRENO VIDAL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1333,73 +1333,73 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>0.07259999999999994</v>
+        <v>-1.260499999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1.0242</v>
+        <v>-2.3907</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9516</v>
+        <v>1.1302</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6665000000000001</v>
+        <v>4.0314</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3723</v>
+        <v>-1.5849</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2943</v>
+        <v>5.6164</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1585000000000001</v>
+        <v>6.6833</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4347</v>
+        <v>0.1304000000000003</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2762</v>
+        <v>6.5529</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5080999999999998</v>
+        <v>-2.6519</v>
       </c>
       <c r="N12" t="n">
-        <v>0.06240000000000001</v>
+        <v>-1.7153</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5705</v>
+        <v>-0.9367000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>2.0548</v>
+        <v>-7.1919</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0274</v>
+        <v>-11.5069</v>
       </c>
       <c r="R12" t="n">
-        <v>3.0822</v>
+        <v>4.3151</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2802</v>
+        <v>1.4</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7923</v>
+        <v>0.8644999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.488</v>
+        <v>0.5354</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.5959</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4178</v>
+        <v>1.5684</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.0137</v>
+        <v>-1.0685</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. KELIKI EBENGO</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1411,73 +1411,73 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.802</v>
+        <v>-6.4308</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.633</v>
+        <v>-7.4274</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1689</v>
+        <v>0.9966000000000003</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7383</v>
+        <v>-2.8869</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3489</v>
+        <v>-2.8957</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0869</v>
+        <v>0.008800000000000807</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7455000000000001</v>
+        <v>1.3169</v>
       </c>
       <c r="K13" t="n">
-        <v>0.351</v>
+        <v>-1.8055</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3945</v>
+        <v>3.1224</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.007300000000000029</v>
+        <v>-4.2038</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6998</v>
+        <v>-1.0901</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6924</v>
+        <v>-3.1136</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.2328</v>
+        <v>-5.7534</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.0822</v>
+        <v>-11.5069</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8494</v>
+        <v>5.753500000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8707</v>
+        <v>1.7299</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9843999999999999</v>
+        <v>0.03669999999999995</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1136</v>
+        <v>1.6933</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.178</v>
+        <v>0.4794000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7192</v>
+        <v>2.726</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.8972</v>
+        <v>-2.2466</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1489,300 +1489,66 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.1641</v>
+        <v>38.8412</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.7608</v>
+        <v>26.9776</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5966000000000001</v>
+        <v>11.8633</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.8629</v>
+        <v>29.8047</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.0252</v>
+        <v>12.2211</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.8378</v>
+        <v>17.5829</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.7657</v>
+        <v>54.2134</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.1248</v>
+        <v>20.9629</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3590999999999998</v>
+        <v>33.2504</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.0972</v>
+        <v>-24.40920000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9004</v>
+        <v>-8.741300000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.1968</v>
+        <v>-15.6675</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8493</v>
+        <v>-14.3838</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.0822</v>
+        <v>-60.61670000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>4.9315</v>
+        <v>46.23310000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4586</v>
+        <v>15.0643</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6387999999999999</v>
+        <v>6.162399999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1801</v>
+        <v>8.9016</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3081</v>
+        <v>8.356000000000002</v>
       </c>
       <c r="W14" t="n">
-        <v>2.7259</v>
+        <v>27.2188</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4178</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>P. CARRENO VIDAL</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>TQ-CB PRAT</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-4.803</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-5.9331</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1.1302</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.489</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-2.1685</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.6574</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.1409</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-0.4532</v>
-      </c>
-      <c r="L15" t="n">
-        <v>3.5942</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-2.6519</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-1.7153</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-0.9367000000000001</v>
-      </c>
-      <c r="P15" t="n">
-        <v>-7.1919</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-11.5069</v>
-      </c>
-      <c r="R15" t="n">
-        <v>4.3151</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.8644999999999999</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.5354</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.5684</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-1.0685</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>S. COSTA I VAZQUEZ</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>TQ-CB PRAT</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-13.4911</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-14.4876</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.9966000000000003</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-9.947100000000001</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-5.8133</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-4.133699999999999</v>
-      </c>
-      <c r="J16" t="n">
-        <v>-5.743300000000001</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-4.7233</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-1.020100000000001</v>
-      </c>
-      <c r="M16" t="n">
-        <v>-4.2038</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-1.0901</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-3.1136</v>
-      </c>
-      <c r="P16" t="n">
-        <v>-5.7534</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-11.5069</v>
-      </c>
-      <c r="R16" t="n">
-        <v>5.753500000000001</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.7299</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.03669999999999995</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.6933</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.4794000000000001</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.726</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-2.2466</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>TQ-CB PRAT</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>4</v>
-      </c>
-      <c r="D17" t="n">
-        <v>38.84120000000001</v>
-      </c>
-      <c r="E17" t="n">
-        <v>26.9777</v>
-      </c>
-      <c r="F17" t="n">
-        <v>11.8633</v>
-      </c>
-      <c r="G17" t="n">
-        <v>29.8048</v>
-      </c>
-      <c r="H17" t="n">
-        <v>12.22139999999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>17.583</v>
-      </c>
-      <c r="J17" t="n">
-        <v>54.2135</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20.963</v>
-      </c>
-      <c r="L17" t="n">
-        <v>33.25069999999999</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-24.40920000000001</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-8.741300000000001</v>
-      </c>
-      <c r="O17" t="n">
-        <v>-15.6675</v>
-      </c>
-      <c r="P17" t="n">
-        <v>-14.3838</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>-60.61670000000001</v>
-      </c>
-      <c r="R17" t="n">
-        <v>46.23310000000001</v>
-      </c>
-      <c r="S17" t="n">
-        <v>15.0643</v>
-      </c>
-      <c r="T17" t="n">
-        <v>6.162399999999999</v>
-      </c>
-      <c r="U17" t="n">
-        <v>8.9016</v>
-      </c>
-      <c r="V17" t="n">
-        <v>8.356000000000002</v>
-      </c>
-      <c r="W17" t="n">
-        <v>27.2188</v>
-      </c>
-      <c r="X17" t="n">
         <v>-18.8628</v>
       </c>
     </row>
